--- a/agent_runs/manjidiwang/episodes/ep15/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep15/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>账本箱被车灯围住（，总时长：13秒，镜头数：5个）</t>
+          <t>账本箱被车灯围住</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>雷军下令废腿（，总时长：10秒，镜头数：3个）</t>
+          <t>雷军下令废腿</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>朱文浩故意吃棍（，总时长：11秒，镜头数：5个）</t>
+          <t>朱文浩故意吃棍</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>录音笔等到证词（，总时长：10秒，镜头数：4个）</t>
+          <t>录音笔等到证词</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>特勤队压制全场（，总时长：10秒，镜头数：4个）</t>
+          <t>特勤队压制全场</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>雷震冲车护子（，总时长：10秒，镜头数：4个）</t>
+          <t>雷震冲车护子</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -372,7 +372,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>朱文浩压住雷震（，总时长：10秒，镜头数：3个）</t>
+          <t>朱文浩压住雷震</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
